--- a/rulesets/example_xlsx/rules.xlsx
+++ b/rulesets/example_xlsx/rules.xlsx
@@ -70,17 +70,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>single_line|electrical_schematic</t>
+          <t>single_line|electrical_schematic|general_supported_electrical</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Floating wire endpoints</t>
+          <t/>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GB 50303-2015 6.1.1</t>
+          <t/>
         </is>
       </c>
     </row>
@@ -107,17 +107,535 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>single_line|electrical_schematic|general_supported_electrical</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>device.duplicate_label</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>device.label_pattern_invalid</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>single_line|electrical_schematic|general_supported_electrical</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>electrical.component_missing_terminals</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>electrical.component_unconnected</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>electrical.transformer_same_net</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>electrical.switch_same_net</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>electrical.switchgear_role_connection</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>single_line|electrical_schematic</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Device label completeness</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>GB 50303-2015 6.1.2</t>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>electrical.switchgear_feed_chain</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>single_line|electrical_schematic</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>electrical.tie_switchgear_dual_side</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>single_line|electrical_schematic</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>electrical.incoming_transformer_busbar_direction</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>{"min_axis_separation": 2.0}</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>single_line</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>electrical.tie_busbar_segment_consistency</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>single_line|electrical_schematic</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>electrical.busbar_underconnected</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>warning</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>{"min_connected_terminals": 2}</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>electrical.branch_box_insufficient_branches</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>{"min_branch_terminals": 2}</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>electrical.relation_unresolved</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t/>
         </is>
       </c>
     </row>
